--- a/naming_conventions.xlsx
+++ b/naming_conventions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e4d3e54824fd230/Documents/GitHub/gr_coding/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e4d3e54824fd230/Documents/GitHub/gr_miscellaneous/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="11_F25DC773A252ABDACC10481B191C69985BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F96E88ED-0ACF-4802-B0D6-465DBEBD21F5}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="11_F25DC773A252ABDACC10481B191C69985BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1777C0C-BAAB-4463-BE3A-3E81A95A6DA1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{611FDBDD-00A8-4FF2-AFD2-267CCD7424D2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{611FDBDD-00A8-4FF2-AFD2-267CCD7424D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="9" r:id="rId1"/>
@@ -2098,6 +2098,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2384,7 +2388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6FABF1-17F7-4B58-BAA4-A445E7E87548}">
-  <sheetPr codeName="Sheet5"/>
+  <sheetPr codeName="Sheet5" filterMode="1"/>
   <dimension ref="A1:E186"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2582,7 +2586,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3364,7 +3368,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3381,7 +3385,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3398,7 +3402,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -3415,7 +3419,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3432,7 +3436,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3449,7 +3453,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3466,7 +3470,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3483,7 +3487,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3500,7 +3504,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3517,7 +3521,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3534,7 +3538,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3551,7 +3555,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3568,7 +3572,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3585,7 +3589,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3602,7 +3606,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3619,7 +3623,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3636,7 +3640,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3653,7 +3657,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3670,7 +3674,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3687,7 +3691,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3704,7 +3708,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3721,7 +3725,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3738,7 +3742,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3755,7 +3759,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -3772,7 +3776,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3789,7 +3793,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3806,7 +3810,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3823,7 +3827,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3840,7 +3844,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3857,7 +3861,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3874,7 +3878,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3891,7 +3895,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3908,7 +3912,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3925,7 +3929,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3942,7 +3946,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3959,7 +3963,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3976,7 +3980,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3993,7 +3997,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -4010,7 +4014,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -4027,7 +4031,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4044,7 +4048,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4061,7 +4065,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4078,7 +4082,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -4095,7 +4099,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -4112,7 +4116,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -4129,7 +4133,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -4146,7 +4150,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -4163,7 +4167,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -4180,7 +4184,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -4197,7 +4201,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -4214,7 +4218,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -4231,7 +4235,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -4248,7 +4252,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -4265,7 +4269,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -4282,7 +4286,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -4299,7 +4303,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -4316,7 +4320,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -4367,7 +4371,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -4384,7 +4388,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -4401,7 +4405,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -4452,7 +4456,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -4605,7 +4609,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -4622,7 +4626,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -4639,7 +4643,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -4656,7 +4660,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -4673,7 +4677,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -4690,7 +4694,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -4724,7 +4728,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -4741,7 +4745,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -4758,7 +4762,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -4775,7 +4779,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -4792,7 +4796,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -4809,7 +4813,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -4826,7 +4830,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -4843,7 +4847,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -4860,7 +4864,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -4877,7 +4881,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -4894,7 +4898,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -4911,7 +4915,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -5030,7 +5034,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -5047,7 +5051,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -5064,7 +5068,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -5081,7 +5085,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -5098,7 +5102,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -5115,7 +5119,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -5132,7 +5136,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -5149,7 +5153,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -5336,7 +5340,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -5353,7 +5357,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -5558,7 +5562,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E186" xr:uid="{9D6FABF1-17F7-4B58-BAA4-A445E7E87548}"/>
+  <autoFilter ref="A1:E186" xr:uid="{9D6FABF1-17F7-4B58-BAA4-A445E7E87548}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="動詞"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/naming_conventions.xlsx
+++ b/naming_conventions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e4d3e54824fd230/Documents/GitHub/gr_miscellaneous/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="11_F25DC773A252ABDACC10481B191C69985BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1777C0C-BAAB-4463-BE3A-3E81A95A6DA1}"/>
+  <xr:revisionPtr revIDLastSave="260" documentId="11_F25DC773A252ABDACC10481B191C69985BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12401EC6-47A9-4217-9187-24385093D1FF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{611FDBDD-00A8-4FF2-AFD2-267CCD7424D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{611FDBDD-00A8-4FF2-AFD2-267CCD7424D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="9" r:id="rId1"/>
@@ -2368,14 +2368,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C22AD30-DFA4-4C9E-BFB5-9210EE48CCA7}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>639</v>
       </c>
@@ -2388,18 +2388,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6FABF1-17F7-4B58-BAA4-A445E7E87548}">
-  <sheetPr codeName="Sheet5" filterMode="1"/>
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:E186"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.4140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" style="6" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>632</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -5562,13 +5562,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E186" xr:uid="{9D6FABF1-17F7-4B58-BAA4-A445E7E87548}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="動詞"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E186" xr:uid="{9D6FABF1-17F7-4B58-BAA4-A445E7E87548}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5578,15 +5572,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B458E02-E553-4B6D-9B79-B3A5574C035E}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>89</v>
       </c>
@@ -5600,7 +5594,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -5614,7 +5608,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -5628,7 +5622,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -5642,7 +5636,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5656,7 +5650,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>50</v>
       </c>
@@ -5670,7 +5664,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5684,7 +5678,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>110</v>
       </c>
@@ -5698,7 +5692,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
@@ -5712,7 +5706,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>118</v>
       </c>
@@ -5726,7 +5720,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>122</v>
       </c>
@@ -5740,7 +5734,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>127</v>
       </c>
@@ -5754,7 +5748,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -5768,7 +5762,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>130</v>
       </c>
@@ -5782,7 +5776,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>132</v>
       </c>
@@ -5796,7 +5790,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>134</v>
       </c>
@@ -5810,7 +5804,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>136</v>
       </c>
@@ -5824,7 +5818,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>138</v>
       </c>
@@ -5838,7 +5832,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>140</v>
       </c>
@@ -5852,7 +5846,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>142</v>
       </c>
@@ -5875,13 +5869,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDCE096-3D94-4FED-A789-441F265D9143}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="73" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>53</v>
       </c>
@@ -5889,7 +5883,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5897,7 +5891,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -5905,7 +5899,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -5913,7 +5907,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>58</v>
       </c>
@@ -5921,7 +5915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>60</v>
       </c>
@@ -5929,7 +5923,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -5937,7 +5931,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -5945,7 +5939,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -5953,7 +5947,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -5961,7 +5955,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>66</v>
       </c>
@@ -5969,7 +5963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -5977,7 +5971,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>70</v>
       </c>
@@ -5985,7 +5979,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>72</v>
       </c>
@@ -5993,7 +5987,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
@@ -6001,7 +5995,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>76</v>
       </c>
@@ -6009,7 +6003,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>78</v>
       </c>
@@ -6017,7 +6011,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>80</v>
       </c>
@@ -6025,7 +6019,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -6033,7 +6027,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>84</v>
       </c>
@@ -6041,7 +6035,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>86</v>
       </c>
@@ -6049,7 +6043,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -6068,19 +6062,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9712444-620E-421C-A7D1-F4997061902E}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.58203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="25.58203125" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="25.58203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="25.58203125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="25.625" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="25.625" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="29.75" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>161</v>
       </c>
@@ -6115,7 +6109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>164</v>
       </c>
@@ -6150,7 +6144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>164</v>
       </c>
@@ -6177,7 +6171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>164</v>
       </c>
@@ -6212,7 +6206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>164</v>
       </c>
@@ -6247,7 +6241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>164</v>
       </c>
@@ -6282,7 +6276,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>170</v>
       </c>
@@ -6317,7 +6311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>170</v>
       </c>
@@ -6352,7 +6346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>170</v>
       </c>
@@ -6377,7 +6371,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>170</v>
       </c>
@@ -6412,7 +6406,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>183</v>
       </c>
@@ -6447,7 +6441,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>183</v>
       </c>
@@ -6482,7 +6476,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>183</v>
       </c>
@@ -6517,7 +6511,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>198</v>
       </c>
@@ -6552,7 +6546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>198</v>
       </c>
@@ -6587,7 +6581,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>198</v>
       </c>
@@ -6622,7 +6616,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>198</v>
       </c>
@@ -6657,7 +6651,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>198</v>
       </c>
@@ -6692,7 +6686,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>212</v>
       </c>
@@ -6727,7 +6721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>212</v>
       </c>
@@ -6762,7 +6756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>212</v>
       </c>
@@ -6797,7 +6791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>212</v>
       </c>
@@ -6832,7 +6826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>212</v>
       </c>
@@ -6857,7 +6851,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>218</v>
       </c>
@@ -6892,7 +6886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>218</v>
       </c>
@@ -6927,7 +6921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>218</v>
       </c>
@@ -6962,7 +6956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>218</v>
       </c>
@@ -6997,7 +6991,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>218</v>
       </c>
@@ -7043,15 +7037,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81DAC327-6DEA-42AA-AAA2-62E67A57DCAA}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.9140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>241</v>
       </c>
@@ -7065,7 +7059,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -7079,7 +7073,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -7093,7 +7087,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>231</v>
       </c>
@@ -7107,7 +7101,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>240</v>
       </c>
@@ -7121,7 +7115,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>237</v>
       </c>
@@ -7135,7 +7129,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>230</v>
       </c>
@@ -7149,7 +7143,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -7163,7 +7157,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>238</v>
       </c>
@@ -7177,7 +7171,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>239</v>
       </c>
@@ -7191,7 +7185,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>235</v>
       </c>
@@ -7205,7 +7199,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
@@ -7219,7 +7213,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>44</v>
       </c>
@@ -7233,7 +7227,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -7247,7 +7241,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -7261,7 +7255,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
